--- a/2027.xlsx
+++ b/2027.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10515"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10919"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2025/Drucken/Section Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{0C105CCB-2D37-B94D-A576-5C7EAC17450C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{BDC7BE5E-AB9D-2442-8E0C-FBEFAFCE953E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1830" windowWidth="23040" windowHeight="7338" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4113" uniqueCount="1438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="1432">
   <si>
     <t>Katalog-Nr</t>
   </si>
@@ -4813,6 +4813,9 @@
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
       <c r="D2" t="s">
         <v>18</v>
       </c>
@@ -4881,6 +4884,9 @@
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
       <c r="D3" t="s">
         <v>36</v>
       </c>
@@ -4946,6 +4952,9 @@
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
@@ -5020,6 +5029,9 @@
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
       <c r="C5" s="2" t="s">
         <v>27</v>
       </c>
@@ -5097,6 +5109,9 @@
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
       <c r="D6" t="s">
         <v>69</v>
       </c>
@@ -5162,6 +5177,9 @@
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
       <c r="C7" t="s">
         <v>27</v>
       </c>
@@ -5239,6 +5257,9 @@
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
       <c r="D8" t="s">
         <v>51</v>
       </c>
@@ -5304,6 +5325,9 @@
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
       <c r="C9" t="s">
         <v>27</v>
       </c>
@@ -5378,6 +5402,9 @@
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
       <c r="C10" t="s">
         <v>27</v>
       </c>
@@ -5438,8 +5465,14 @@
       <c r="Y10" t="s">
         <v>35</v>
       </c>
+      <c r="AA10" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
       <c r="C11" t="s">
         <v>27</v>
       </c>
@@ -5514,6 +5547,9 @@
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
       <c r="C12" t="s">
         <v>27</v>
       </c>
@@ -5588,6 +5624,9 @@
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
       <c r="D13" t="s">
         <v>108</v>
       </c>
@@ -5650,6 +5689,9 @@
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
       <c r="C14" t="s">
         <v>27</v>
       </c>
@@ -5709,6 +5751,9 @@
       </c>
       <c r="Y14" t="s">
         <v>35</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
@@ -8089,7 +8134,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D49" t="s">
         <v>416</v>
       </c>
@@ -8154,7 +8199,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D50" t="s">
         <v>421</v>
       </c>
@@ -8225,7 +8270,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D51" t="s">
         <v>426</v>
       </c>
@@ -8290,7 +8335,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C52" t="s">
         <v>27</v>
       </c>
@@ -8364,7 +8409,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D53" t="s">
         <v>439</v>
       </c>
@@ -8435,7 +8480,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D54" t="s">
         <v>450</v>
       </c>
@@ -8506,7 +8551,10 @@
         <v>162</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B55" t="s">
+        <v>27</v>
+      </c>
       <c r="C55" t="s">
         <v>27</v>
       </c>
@@ -8580,7 +8628,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D56" t="s">
         <v>461</v>
       </c>
@@ -8645,7 +8693,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D57" t="s">
         <v>465</v>
       </c>
@@ -8719,7 +8767,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B58" t="s">
+        <v>27</v>
+      </c>
       <c r="C58" t="s">
         <v>27</v>
       </c>
@@ -8793,7 +8844,10 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B59" t="s">
+        <v>27</v>
+      </c>
       <c r="C59" t="s">
         <v>27</v>
       </c>
@@ -8870,7 +8924,10 @@
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B60" t="s">
+        <v>27</v>
+      </c>
       <c r="C60" t="s">
         <v>27</v>
       </c>
@@ -8932,7 +8989,10 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B61" t="s">
+        <v>27</v>
+      </c>
       <c r="C61" t="s">
         <v>27</v>
       </c>
@@ -9009,7 +9069,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D62" t="s">
         <v>511</v>
       </c>
@@ -9080,7 +9140,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B63" t="s">
+        <v>27</v>
+      </c>
       <c r="C63" t="s">
         <v>27</v>
       </c>
@@ -9154,7 +9217,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B64" t="s">
+        <v>27</v>
+      </c>
       <c r="C64" t="s">
         <v>27</v>
       </c>
@@ -9228,7 +9294,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="65" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D65" t="s">
         <v>543</v>
       </c>
@@ -9299,7 +9365,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="66" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B66" t="s">
+        <v>27</v>
+      </c>
       <c r="C66" t="s">
         <v>27</v>
       </c>
@@ -9373,7 +9442,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B67" t="s">
+        <v>27</v>
+      </c>
       <c r="C67" t="s">
         <v>27</v>
       </c>
@@ -9435,7 +9507,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="68" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D68" t="s">
         <v>565</v>
       </c>
@@ -9494,7 +9566,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="69" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B69" t="s">
+        <v>27</v>
+      </c>
       <c r="C69" t="s">
         <v>27</v>
       </c>
@@ -9559,7 +9634,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="70" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B70" t="s">
+        <v>27</v>
+      </c>
       <c r="C70" t="s">
         <v>27</v>
       </c>
@@ -9636,7 +9714,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="71" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D71" t="s">
         <v>592</v>
       </c>
@@ -9707,7 +9785,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="72" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B72" t="s">
+        <v>27</v>
+      </c>
       <c r="C72" t="s">
         <v>27</v>
       </c>
@@ -9781,7 +9862,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="73" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D73" t="s">
         <v>603</v>
       </c>
@@ -9852,7 +9933,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="74" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B74" t="s">
+        <v>27</v>
+      </c>
       <c r="C74" t="s">
         <v>27</v>
       </c>
@@ -9926,7 +10010,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="75" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B75" t="s">
+        <v>27</v>
+      </c>
       <c r="C75" t="s">
         <v>27</v>
       </c>
@@ -9988,7 +10075,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="76" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B76" t="s">
+        <v>27</v>
+      </c>
       <c r="C76" t="s">
         <v>27</v>
       </c>
@@ -10050,7 +10140,10 @@
         <v>162</v>
       </c>
     </row>
-    <row r="77" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B77" t="s">
+        <v>27</v>
+      </c>
       <c r="C77" t="s">
         <v>27</v>
       </c>
@@ -10124,7 +10217,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D78" t="s">
         <v>647</v>
       </c>
@@ -10195,7 +10288,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="79" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D79" t="s">
         <v>652</v>
       </c>
@@ -10266,7 +10359,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="80" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D80" t="s">
         <v>660</v>
       </c>
@@ -10337,7 +10430,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D81" t="s">
         <v>666</v>
       </c>
@@ -10408,7 +10501,10 @@
         <v>162</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B82" t="s">
+        <v>27</v>
+      </c>
       <c r="C82" t="s">
         <v>27</v>
       </c>
@@ -10473,7 +10569,10 @@
         <v>35</v>
       </c>
     </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B83" t="s">
+        <v>27</v>
+      </c>
       <c r="C83" t="s">
         <v>27</v>
       </c>
@@ -10547,7 +10646,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D84" t="s">
         <v>688</v>
       </c>
@@ -10612,7 +10711,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D85" t="s">
         <v>695</v>
       </c>
@@ -10683,7 +10782,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B86" t="s">
+        <v>27</v>
+      </c>
       <c r="C86" t="s">
         <v>27</v>
       </c>
@@ -10757,7 +10859,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D87" t="s">
         <v>705</v>
       </c>
@@ -10828,7 +10930,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D88" t="s">
         <v>717</v>
       </c>
@@ -10887,7 +10989,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D89" t="s">
         <v>726</v>
       </c>
@@ -10958,7 +11060,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D90" t="s">
         <v>736</v>
       </c>
@@ -11029,7 +11131,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D91" t="s">
         <v>741</v>
       </c>
@@ -11100,7 +11202,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B92" t="s">
+        <v>27</v>
+      </c>
       <c r="C92" t="s">
         <v>27</v>
       </c>
@@ -11174,7 +11279,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B93" t="s">
+        <v>27</v>
+      </c>
       <c r="C93" t="s">
         <v>27</v>
       </c>
@@ -11248,7 +11356,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D94" t="s">
         <v>766</v>
       </c>
@@ -11319,7 +11427,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D95" t="s">
         <v>772</v>
       </c>
@@ -11390,7 +11498,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D96" t="s">
         <v>777</v>
       </c>

--- a/2027.xlsx
+++ b/2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2025/Drucken/Section Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{BDC7BE5E-AB9D-2442-8E0C-FBEFAFCE953E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{D787E4CA-058C-F043-AC37-9558793B5EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1830" windowWidth="23040" windowHeight="7338" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="1432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4151" uniqueCount="1434">
   <si>
     <t>Katalog-Nr</t>
   </si>
@@ -4331,6 +4331,9 @@
   </si>
   <si>
     <t>Show C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabio Brambilla </t>
   </si>
 </sst>
 </file>
@@ -4880,7 +4883,7 @@
         <v>35</v>
       </c>
       <c r="AA2" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -5025,7 +5028,7 @@
         <v>35</v>
       </c>
       <c r="AA4" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
@@ -5105,7 +5108,7 @@
         <v>43</v>
       </c>
       <c r="AA5" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
@@ -5173,7 +5176,7 @@
         <v>35</v>
       </c>
       <c r="AA6" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
@@ -5253,7 +5256,7 @@
         <v>43</v>
       </c>
       <c r="AA7" t="s">
-        <v>43</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
@@ -5321,7 +5324,7 @@
         <v>35</v>
       </c>
       <c r="AA8" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
@@ -5398,7 +5401,7 @@
         <v>35</v>
       </c>
       <c r="AA9" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
@@ -5543,7 +5546,7 @@
         <v>43</v>
       </c>
       <c r="AA11" t="s">
-        <v>43</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
@@ -5620,7 +5623,7 @@
         <v>43</v>
       </c>
       <c r="AA12" t="s">
-        <v>43</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
@@ -5686,6 +5689,9 @@
       </c>
       <c r="Y13" t="s">
         <v>35</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
@@ -5824,7 +5830,7 @@
         <v>35</v>
       </c>
       <c r="AA15" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
@@ -5895,7 +5901,7 @@
         <v>35</v>
       </c>
       <c r="AA16" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="17" spans="3:27" x14ac:dyDescent="0.2">
@@ -5966,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="AA17" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="18" spans="3:27" x14ac:dyDescent="0.2">
@@ -6031,7 +6037,7 @@
         <v>35</v>
       </c>
       <c r="AA18" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="19" spans="3:27" x14ac:dyDescent="0.2">
@@ -6105,7 +6111,7 @@
         <v>57</v>
       </c>
       <c r="AA19" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="3:27" x14ac:dyDescent="0.2">
@@ -6176,7 +6182,7 @@
         <v>57</v>
       </c>
       <c r="AA20" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="3:27" x14ac:dyDescent="0.2">
@@ -6247,7 +6253,7 @@
         <v>57</v>
       </c>
       <c r="AA21" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="3:27" x14ac:dyDescent="0.2">
@@ -6312,7 +6318,7 @@
         <v>57</v>
       </c>
       <c r="AA22" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="3:27" x14ac:dyDescent="0.2">
@@ -6377,7 +6383,7 @@
         <v>57</v>
       </c>
       <c r="AA23" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="3:27" x14ac:dyDescent="0.2">
@@ -6445,7 +6451,7 @@
         <v>57</v>
       </c>
       <c r="AA24" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="3:27" x14ac:dyDescent="0.2">
@@ -6516,7 +6522,7 @@
         <v>57</v>
       </c>
       <c r="AA25" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="3:27" x14ac:dyDescent="0.2">
@@ -6590,7 +6596,7 @@
         <v>57</v>
       </c>
       <c r="AA26" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="3:27" x14ac:dyDescent="0.2">
@@ -6664,7 +6670,7 @@
         <v>57</v>
       </c>
       <c r="AA27" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="3:27" x14ac:dyDescent="0.2">
@@ -6806,7 +6812,7 @@
         <v>162</v>
       </c>
       <c r="AA29" t="s">
-        <v>162</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="30" spans="3:27" x14ac:dyDescent="0.2">
@@ -6871,7 +6877,7 @@
         <v>162</v>
       </c>
       <c r="AA30" t="s">
-        <v>162</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="31" spans="3:27" x14ac:dyDescent="0.2">
@@ -6945,7 +6951,7 @@
         <v>162</v>
       </c>
       <c r="AA31" t="s">
-        <v>162</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="32" spans="3:27" x14ac:dyDescent="0.2">
@@ -7016,7 +7022,7 @@
         <v>162</v>
       </c>
       <c r="AA32" t="s">
-        <v>162</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="33" spans="3:27" x14ac:dyDescent="0.2">
@@ -7087,7 +7093,7 @@
         <v>277</v>
       </c>
       <c r="AA33" t="s">
-        <v>277</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="3:27" x14ac:dyDescent="0.2">
@@ -7158,7 +7164,7 @@
         <v>277</v>
       </c>
       <c r="AA34" t="s">
-        <v>277</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="3:27" x14ac:dyDescent="0.2">
@@ -7232,7 +7238,7 @@
         <v>277</v>
       </c>
       <c r="AA35" t="s">
-        <v>277</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="3:27" x14ac:dyDescent="0.2">
@@ -7297,7 +7303,7 @@
         <v>277</v>
       </c>
       <c r="AA36" t="s">
-        <v>277</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="3:27" x14ac:dyDescent="0.2">
@@ -7371,7 +7377,7 @@
         <v>277</v>
       </c>
       <c r="AA37" t="s">
-        <v>277</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="3:27" x14ac:dyDescent="0.2">
@@ -7442,7 +7448,7 @@
         <v>277</v>
       </c>
       <c r="AA38" t="s">
-        <v>277</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="3:27" x14ac:dyDescent="0.2">
@@ -7513,7 +7519,7 @@
         <v>35</v>
       </c>
       <c r="AA39" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="3:27" x14ac:dyDescent="0.2">
@@ -7578,7 +7584,7 @@
         <v>35</v>
       </c>
       <c r="AA40" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="3:27" x14ac:dyDescent="0.2">
@@ -7655,7 +7661,7 @@
         <v>43</v>
       </c>
       <c r="AA41" t="s">
-        <v>43</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42" spans="3:27" x14ac:dyDescent="0.2">
@@ -7726,7 +7732,7 @@
         <v>43</v>
       </c>
       <c r="AA42" t="s">
-        <v>43</v>
+        <v>162</v>
       </c>
     </row>
     <row r="43" spans="3:27" x14ac:dyDescent="0.2">
@@ -7791,7 +7797,7 @@
         <v>43</v>
       </c>
       <c r="AA43" t="s">
-        <v>43</v>
+        <v>162</v>
       </c>
     </row>
     <row r="44" spans="3:27" x14ac:dyDescent="0.2">
@@ -7856,7 +7862,7 @@
         <v>43</v>
       </c>
       <c r="AA44" t="s">
-        <v>43</v>
+        <v>162</v>
       </c>
     </row>
     <row r="45" spans="3:27" x14ac:dyDescent="0.2">
@@ -7921,7 +7927,7 @@
         <v>43</v>
       </c>
       <c r="AA45" t="s">
-        <v>43</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" spans="3:27" x14ac:dyDescent="0.2">
@@ -7995,7 +8001,7 @@
         <v>43</v>
       </c>
       <c r="AA46" t="s">
-        <v>43</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="3:27" x14ac:dyDescent="0.2">
@@ -8066,7 +8072,7 @@
         <v>43</v>
       </c>
       <c r="AA47" t="s">
-        <v>43</v>
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="3:27" x14ac:dyDescent="0.2">
@@ -8131,7 +8137,7 @@
         <v>43</v>
       </c>
       <c r="AA48" t="s">
-        <v>43</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49" spans="2:27" x14ac:dyDescent="0.2">
@@ -8196,7 +8202,7 @@
         <v>43</v>
       </c>
       <c r="AA49" t="s">
-        <v>43</v>
+        <v>162</v>
       </c>
     </row>
     <row r="50" spans="2:27" x14ac:dyDescent="0.2">
@@ -8267,7 +8273,7 @@
         <v>43</v>
       </c>
       <c r="AA50" t="s">
-        <v>43</v>
+        <v>162</v>
       </c>
     </row>
     <row r="51" spans="2:27" x14ac:dyDescent="0.2">
@@ -8332,7 +8338,7 @@
         <v>162</v>
       </c>
       <c r="AA51" t="s">
-        <v>162</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="52" spans="2:27" x14ac:dyDescent="0.2">
@@ -8406,7 +8412,7 @@
         <v>162</v>
       </c>
       <c r="AA52" t="s">
-        <v>162</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="53" spans="2:27" x14ac:dyDescent="0.2">
@@ -8477,7 +8483,7 @@
         <v>162</v>
       </c>
       <c r="AA53" t="s">
-        <v>162</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="54" spans="2:27" x14ac:dyDescent="0.2">
@@ -8548,7 +8554,7 @@
         <v>162</v>
       </c>
       <c r="AA54" t="s">
-        <v>162</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="55" spans="2:27" x14ac:dyDescent="0.2">
@@ -8625,7 +8631,7 @@
         <v>162</v>
       </c>
       <c r="AA55" t="s">
-        <v>162</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="56" spans="2:27" x14ac:dyDescent="0.2">
@@ -8690,7 +8696,7 @@
         <v>162</v>
       </c>
       <c r="AA56" t="s">
-        <v>162</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57" spans="2:27" x14ac:dyDescent="0.2">
@@ -8764,7 +8770,7 @@
         <v>277</v>
       </c>
       <c r="AA57" t="s">
-        <v>277</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58" spans="2:27" x14ac:dyDescent="0.2">
@@ -8841,7 +8847,7 @@
         <v>35</v>
       </c>
       <c r="AA58" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="59" spans="2:27" x14ac:dyDescent="0.2">
@@ -8921,7 +8927,7 @@
         <v>35</v>
       </c>
       <c r="AA59" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="60" spans="2:27" x14ac:dyDescent="0.2">
@@ -9066,7 +9072,7 @@
         <v>57</v>
       </c>
       <c r="AA61" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
     </row>
     <row r="62" spans="2:27" x14ac:dyDescent="0.2">
@@ -9137,7 +9143,7 @@
         <v>57</v>
       </c>
       <c r="AA62" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
     </row>
     <row r="63" spans="2:27" x14ac:dyDescent="0.2">
@@ -9214,7 +9220,7 @@
         <v>57</v>
       </c>
       <c r="AA63" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
     </row>
     <row r="64" spans="2:27" x14ac:dyDescent="0.2">
@@ -9291,7 +9297,7 @@
         <v>57</v>
       </c>
       <c r="AA64" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
     </row>
     <row r="65" spans="2:27" x14ac:dyDescent="0.2">
@@ -9362,7 +9368,7 @@
         <v>57</v>
       </c>
       <c r="AA65" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
     </row>
     <row r="66" spans="2:27" x14ac:dyDescent="0.2">
@@ -9439,7 +9445,7 @@
         <v>57</v>
       </c>
       <c r="AA66" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
     </row>
     <row r="67" spans="2:27" x14ac:dyDescent="0.2">
@@ -9711,7 +9717,7 @@
         <v>277</v>
       </c>
       <c r="AA70" t="s">
-        <v>277</v>
+        <v>162</v>
       </c>
     </row>
     <row r="71" spans="2:27" x14ac:dyDescent="0.2">
@@ -9782,7 +9788,7 @@
         <v>277</v>
       </c>
       <c r="AA71" t="s">
-        <v>277</v>
+        <v>162</v>
       </c>
     </row>
     <row r="72" spans="2:27" x14ac:dyDescent="0.2">
@@ -9859,7 +9865,7 @@
         <v>277</v>
       </c>
       <c r="AA72" t="s">
-        <v>277</v>
+        <v>162</v>
       </c>
     </row>
     <row r="73" spans="2:27" x14ac:dyDescent="0.2">
@@ -9930,7 +9936,7 @@
         <v>277</v>
       </c>
       <c r="AA73" t="s">
-        <v>277</v>
+        <v>162</v>
       </c>
     </row>
     <row r="74" spans="2:27" x14ac:dyDescent="0.2">
@@ -10007,7 +10013,7 @@
         <v>277</v>
       </c>
       <c r="AA74" t="s">
-        <v>277</v>
+        <v>162</v>
       </c>
     </row>
     <row r="75" spans="2:27" x14ac:dyDescent="0.2">
@@ -10214,7 +10220,7 @@
         <v>35</v>
       </c>
       <c r="AA77" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="78" spans="2:27" x14ac:dyDescent="0.2">
@@ -10285,7 +10291,7 @@
         <v>35</v>
       </c>
       <c r="AA78" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="79" spans="2:27" x14ac:dyDescent="0.2">
@@ -10356,7 +10362,7 @@
         <v>162</v>
       </c>
       <c r="AA79" t="s">
-        <v>162</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="80" spans="2:27" x14ac:dyDescent="0.2">
@@ -10427,7 +10433,7 @@
         <v>162</v>
       </c>
       <c r="AA80" t="s">
-        <v>162</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="81" spans="2:27" x14ac:dyDescent="0.2">
@@ -10498,7 +10504,7 @@
         <v>162</v>
       </c>
       <c r="AA81" t="s">
-        <v>162</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="82" spans="2:27" x14ac:dyDescent="0.2">
@@ -10643,7 +10649,7 @@
         <v>162</v>
       </c>
       <c r="AA83" t="s">
-        <v>162</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="84" spans="2:27" x14ac:dyDescent="0.2">
@@ -10708,7 +10714,7 @@
         <v>277</v>
       </c>
       <c r="AA84" t="s">
-        <v>277</v>
+        <v>43</v>
       </c>
     </row>
     <row r="85" spans="2:27" x14ac:dyDescent="0.2">
@@ -10779,7 +10785,7 @@
         <v>277</v>
       </c>
       <c r="AA85" t="s">
-        <v>277</v>
+        <v>43</v>
       </c>
     </row>
     <row r="86" spans="2:27" x14ac:dyDescent="0.2">
@@ -10856,7 +10862,7 @@
         <v>277</v>
       </c>
       <c r="AA86" t="s">
-        <v>277</v>
+        <v>43</v>
       </c>
     </row>
     <row r="87" spans="2:27" x14ac:dyDescent="0.2">
@@ -10927,7 +10933,7 @@
         <v>35</v>
       </c>
       <c r="AA87" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="88" spans="2:27" x14ac:dyDescent="0.2">
@@ -11057,7 +11063,7 @@
         <v>35</v>
       </c>
       <c r="AA89" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="90" spans="2:27" x14ac:dyDescent="0.2">
@@ -11128,7 +11134,7 @@
         <v>277</v>
       </c>
       <c r="AA90" t="s">
-        <v>277</v>
+        <v>57</v>
       </c>
     </row>
     <row r="91" spans="2:27" x14ac:dyDescent="0.2">
@@ -11199,7 +11205,7 @@
         <v>277</v>
       </c>
       <c r="AA91" t="s">
-        <v>277</v>
+        <v>57</v>
       </c>
     </row>
     <row r="92" spans="2:27" x14ac:dyDescent="0.2">
@@ -11276,7 +11282,7 @@
         <v>277</v>
       </c>
       <c r="AA92" t="s">
-        <v>277</v>
+        <v>57</v>
       </c>
     </row>
     <row r="93" spans="2:27" x14ac:dyDescent="0.2">
@@ -11353,7 +11359,7 @@
         <v>277</v>
       </c>
       <c r="AA93" t="s">
-        <v>277</v>
+        <v>57</v>
       </c>
     </row>
     <row r="94" spans="2:27" x14ac:dyDescent="0.2">
@@ -11424,7 +11430,7 @@
         <v>57</v>
       </c>
       <c r="AA94" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="95" spans="2:27" x14ac:dyDescent="0.2">
@@ -11495,7 +11501,7 @@
         <v>57</v>
       </c>
       <c r="AA95" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96" spans="2:27" x14ac:dyDescent="0.2">
@@ -11566,7 +11572,7 @@
         <v>57</v>
       </c>
       <c r="AA96" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="97" spans="3:27" x14ac:dyDescent="0.2">
@@ -11640,7 +11646,7 @@
         <v>162</v>
       </c>
       <c r="AA97" t="s">
-        <v>162</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="98" spans="3:27" x14ac:dyDescent="0.2">
@@ -11701,6 +11707,9 @@
       <c r="Y98" t="s">
         <v>277</v>
       </c>
+      <c r="AA98" t="s">
+        <v>1432</v>
+      </c>
     </row>
     <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" t="s">
@@ -11773,7 +11782,7 @@
         <v>162</v>
       </c>
       <c r="AA99" t="s">
-        <v>162</v>
+        <v>57</v>
       </c>
     </row>
     <row r="100" spans="3:27" x14ac:dyDescent="0.2">
@@ -11844,7 +11853,7 @@
         <v>162</v>
       </c>
       <c r="AA100" t="s">
-        <v>162</v>
+        <v>57</v>
       </c>
     </row>
     <row r="101" spans="3:27" x14ac:dyDescent="0.2">
@@ -11918,7 +11927,7 @@
         <v>162</v>
       </c>
       <c r="AA101" t="s">
-        <v>162</v>
+        <v>43</v>
       </c>
     </row>
     <row r="102" spans="3:27" x14ac:dyDescent="0.2">
@@ -11983,7 +11992,7 @@
         <v>162</v>
       </c>
       <c r="AA102" t="s">
-        <v>162</v>
+        <v>43</v>
       </c>
     </row>
     <row r="103" spans="3:27" x14ac:dyDescent="0.2">
@@ -12048,7 +12057,7 @@
         <v>162</v>
       </c>
       <c r="AA103" t="s">
-        <v>162</v>
+        <v>43</v>
       </c>
     </row>
     <row r="104" spans="3:27" x14ac:dyDescent="0.2">
@@ -12122,7 +12131,7 @@
         <v>162</v>
       </c>
       <c r="AA104" t="s">
-        <v>162</v>
+        <v>43</v>
       </c>
     </row>
     <row r="105" spans="3:27" x14ac:dyDescent="0.2">
@@ -12196,7 +12205,7 @@
         <v>277</v>
       </c>
       <c r="AA105" t="s">
-        <v>277</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="106" spans="3:27" x14ac:dyDescent="0.2">
@@ -12273,7 +12282,7 @@
         <v>57</v>
       </c>
       <c r="AA106" t="s">
-        <v>57</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="107" spans="3:27" x14ac:dyDescent="0.2">
@@ -12338,7 +12347,7 @@
         <v>57</v>
       </c>
       <c r="AA107" t="s">
-        <v>57</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="108" spans="3:27" x14ac:dyDescent="0.2">
@@ -12468,7 +12477,7 @@
         <v>162</v>
       </c>
       <c r="AA109" t="s">
-        <v>162</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="110" spans="3:27" x14ac:dyDescent="0.2">
@@ -12539,7 +12548,7 @@
         <v>277</v>
       </c>
       <c r="AA110" t="s">
-        <v>277</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="111" spans="3:27" x14ac:dyDescent="0.2">
@@ -12616,7 +12625,7 @@
         <v>57</v>
       </c>
       <c r="AA111" t="s">
-        <v>57</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="112" spans="3:27" x14ac:dyDescent="0.2">
@@ -12690,7 +12699,7 @@
         <v>57</v>
       </c>
       <c r="AA112" t="s">
-        <v>57</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="113" spans="3:27" x14ac:dyDescent="0.2">
@@ -12764,7 +12773,7 @@
         <v>57</v>
       </c>
       <c r="AA113" t="s">
-        <v>57</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="114" spans="3:27" x14ac:dyDescent="0.2">
@@ -12829,7 +12838,7 @@
         <v>277</v>
       </c>
       <c r="AA114" t="s">
-        <v>277</v>
+        <v>57</v>
       </c>
     </row>
     <row r="115" spans="3:27" x14ac:dyDescent="0.2">
@@ -12894,7 +12903,7 @@
         <v>162</v>
       </c>
       <c r="AA115" t="s">
-        <v>162</v>
+        <v>57</v>
       </c>
     </row>
     <row r="116" spans="3:27" x14ac:dyDescent="0.2">
@@ -12959,7 +12968,7 @@
         <v>57</v>
       </c>
       <c r="AA116" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="117" spans="3:27" x14ac:dyDescent="0.2">
@@ -13030,7 +13039,7 @@
         <v>43</v>
       </c>
       <c r="AA117" t="s">
-        <v>43</v>
+        <v>277</v>
       </c>
     </row>
     <row r="118" spans="3:27" x14ac:dyDescent="0.2">
@@ -13098,7 +13107,7 @@
         <v>43</v>
       </c>
       <c r="AA118" t="s">
-        <v>43</v>
+        <v>277</v>
       </c>
     </row>
     <row r="119" spans="3:27" x14ac:dyDescent="0.2">
@@ -13163,7 +13172,7 @@
         <v>277</v>
       </c>
       <c r="AA119" t="s">
-        <v>277</v>
+        <v>43</v>
       </c>
     </row>
     <row r="120" spans="3:27" x14ac:dyDescent="0.2">
@@ -13228,7 +13237,7 @@
         <v>277</v>
       </c>
       <c r="AA120" t="s">
-        <v>277</v>
+        <v>43</v>
       </c>
     </row>
     <row r="121" spans="3:27" x14ac:dyDescent="0.2">
@@ -13293,7 +13302,7 @@
         <v>57</v>
       </c>
       <c r="AA121" t="s">
-        <v>57</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="122" spans="3:27" x14ac:dyDescent="0.2">
@@ -13364,7 +13373,7 @@
         <v>277</v>
       </c>
       <c r="AA122" t="s">
-        <v>277</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="123" spans="3:27" x14ac:dyDescent="0.2">
@@ -13435,7 +13444,7 @@
         <v>277</v>
       </c>
       <c r="AA123" t="s">
-        <v>277</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="124" spans="3:27" x14ac:dyDescent="0.2">
@@ -13506,7 +13515,7 @@
         <v>57</v>
       </c>
       <c r="AA124" t="s">
-        <v>57</v>
+        <v>277</v>
       </c>
     </row>
     <row r="125" spans="3:27" x14ac:dyDescent="0.2">
@@ -13577,7 +13586,7 @@
         <v>57</v>
       </c>
       <c r="AA125" t="s">
-        <v>57</v>
+        <v>277</v>
       </c>
     </row>
     <row r="126" spans="3:27" x14ac:dyDescent="0.2">
@@ -13651,7 +13660,7 @@
         <v>57</v>
       </c>
       <c r="AA126" t="s">
-        <v>57</v>
+        <v>277</v>
       </c>
     </row>
     <row r="127" spans="3:27" x14ac:dyDescent="0.2">
@@ -13722,7 +13731,7 @@
         <v>57</v>
       </c>
       <c r="AA127" t="s">
-        <v>57</v>
+        <v>277</v>
       </c>
     </row>
     <row r="128" spans="3:27" x14ac:dyDescent="0.2">
@@ -13846,7 +13855,7 @@
         <v>277</v>
       </c>
       <c r="AA129" t="s">
-        <v>277</v>
+        <v>57</v>
       </c>
     </row>
     <row r="130" spans="3:27" x14ac:dyDescent="0.2">
@@ -13920,7 +13929,7 @@
         <v>277</v>
       </c>
       <c r="AA130" t="s">
-        <v>277</v>
+        <v>57</v>
       </c>
     </row>
     <row r="131" spans="3:27" x14ac:dyDescent="0.2">
@@ -14053,7 +14062,7 @@
         <v>277</v>
       </c>
       <c r="AA132" t="s">
-        <v>277</v>
+        <v>57</v>
       </c>
     </row>
     <row r="133" spans="3:27" x14ac:dyDescent="0.2">
@@ -14124,7 +14133,7 @@
         <v>277</v>
       </c>
       <c r="AA133" t="s">
-        <v>277</v>
+        <v>57</v>
       </c>
     </row>
     <row r="134" spans="3:27" x14ac:dyDescent="0.2">
@@ -14257,7 +14266,7 @@
         <v>277</v>
       </c>
       <c r="AA135" t="s">
-        <v>277</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="136" spans="3:27" x14ac:dyDescent="0.2">
@@ -14458,7 +14467,7 @@
         <v>43</v>
       </c>
       <c r="AA138" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="139" spans="3:27" x14ac:dyDescent="0.2">
@@ -14529,7 +14538,7 @@
         <v>43</v>
       </c>
       <c r="AA139" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="140" spans="3:27" x14ac:dyDescent="0.2">
@@ -14600,7 +14609,7 @@
         <v>43</v>
       </c>
       <c r="AA140" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="141" spans="3:27" x14ac:dyDescent="0.2">
@@ -14668,7 +14677,7 @@
         <v>43</v>
       </c>
       <c r="AA141" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="142" spans="3:27" x14ac:dyDescent="0.2">
@@ -14739,7 +14748,7 @@
         <v>43</v>
       </c>
       <c r="AA142" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="143" spans="3:27" x14ac:dyDescent="0.2">
@@ -14807,7 +14816,7 @@
         <v>43</v>
       </c>
       <c r="AA143" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="144" spans="3:27" x14ac:dyDescent="0.2">
@@ -14872,7 +14881,7 @@
         <v>43</v>
       </c>
       <c r="AA144" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="145" spans="3:27" x14ac:dyDescent="0.2">
@@ -14949,7 +14958,7 @@
         <v>43</v>
       </c>
       <c r="AA145" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="146" spans="3:27" x14ac:dyDescent="0.2">
@@ -15082,7 +15091,7 @@
         <v>277</v>
       </c>
       <c r="AA147" t="s">
-        <v>277</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="148" spans="3:27" x14ac:dyDescent="0.2">
@@ -15156,7 +15165,7 @@
         <v>277</v>
       </c>
       <c r="AA148" t="s">
-        <v>277</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="149" spans="3:27" x14ac:dyDescent="0.2">
@@ -15230,7 +15239,7 @@
         <v>277</v>
       </c>
       <c r="AA149" t="s">
-        <v>277</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="150" spans="3:27" x14ac:dyDescent="0.2">
@@ -15301,7 +15310,7 @@
         <v>277</v>
       </c>
       <c r="AA150" t="s">
-        <v>277</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="151" spans="3:27" x14ac:dyDescent="0.2">
@@ -15375,7 +15384,7 @@
         <v>162</v>
       </c>
       <c r="AA151" t="s">
-        <v>162</v>
+        <v>43</v>
       </c>
     </row>
     <row r="152" spans="3:27" x14ac:dyDescent="0.2">
@@ -15570,7 +15579,7 @@
         <v>162</v>
       </c>
       <c r="AA154" t="s">
-        <v>162</v>
+        <v>277</v>
       </c>
     </row>
     <row r="155" spans="3:27" x14ac:dyDescent="0.2">
@@ -15635,7 +15644,7 @@
         <v>162</v>
       </c>
       <c r="AA155" t="s">
-        <v>162</v>
+        <v>277</v>
       </c>
     </row>
     <row r="156" spans="3:27" x14ac:dyDescent="0.2">
@@ -15771,7 +15780,7 @@
         <v>162</v>
       </c>
       <c r="AA157" t="s">
-        <v>162</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="158" spans="3:27" x14ac:dyDescent="0.2">
@@ -15910,7 +15919,7 @@
         <v>35</v>
       </c>
       <c r="AA159" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="160" spans="3:27" x14ac:dyDescent="0.2">
@@ -15984,7 +15993,7 @@
         <v>35</v>
       </c>
       <c r="AA160" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="161" spans="3:27" x14ac:dyDescent="0.2">
@@ -16179,7 +16188,7 @@
         <v>35</v>
       </c>
       <c r="AA163" t="s">
-        <v>35</v>
+        <v>277</v>
       </c>
     </row>
     <row r="164" spans="3:27" x14ac:dyDescent="0.2">
@@ -16250,7 +16259,7 @@
         <v>43</v>
       </c>
       <c r="AA164" t="s">
-        <v>43</v>
+        <v>277</v>
       </c>
     </row>
     <row r="165" spans="3:27" x14ac:dyDescent="0.2">
@@ -16324,7 +16333,7 @@
         <v>43</v>
       </c>
       <c r="AA165" t="s">
-        <v>43</v>
+        <v>277</v>
       </c>
     </row>
     <row r="166" spans="3:27" x14ac:dyDescent="0.2">
@@ -16398,7 +16407,7 @@
         <v>162</v>
       </c>
       <c r="AA166" t="s">
-        <v>162</v>
+        <v>277</v>
       </c>
     </row>
     <row r="167" spans="3:27" x14ac:dyDescent="0.2">
@@ -16469,7 +16478,7 @@
         <v>162</v>
       </c>
       <c r="AA167" t="s">
-        <v>162</v>
+        <v>277</v>
       </c>
     </row>
     <row r="168" spans="3:27" x14ac:dyDescent="0.2">
@@ -16723,7 +16732,7 @@
         <v>35</v>
       </c>
       <c r="AA171" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="172" spans="3:27" x14ac:dyDescent="0.2">
@@ -16794,7 +16803,7 @@
         <v>35</v>
       </c>
       <c r="AA172" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="173" spans="3:27" x14ac:dyDescent="0.2">
@@ -16865,7 +16874,7 @@
         <v>35</v>
       </c>
       <c r="AA173" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="174" spans="3:27" x14ac:dyDescent="0.2">
@@ -16939,7 +16948,7 @@
         <v>35</v>
       </c>
       <c r="AA174" t="s">
-        <v>35</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="175" spans="3:27" x14ac:dyDescent="0.2">
@@ -17013,7 +17022,7 @@
         <v>43</v>
       </c>
       <c r="AA175" t="s">
-        <v>43</v>
+        <v>277</v>
       </c>
     </row>
     <row r="176" spans="3:27" x14ac:dyDescent="0.2">
@@ -17084,7 +17093,7 @@
         <v>43</v>
       </c>
       <c r="AA176" t="s">
-        <v>43</v>
+        <v>277</v>
       </c>
     </row>
     <row r="177" spans="3:27" x14ac:dyDescent="0.2">
@@ -17158,7 +17167,7 @@
         <v>43</v>
       </c>
       <c r="AA177" t="s">
-        <v>43</v>
+        <v>277</v>
       </c>
     </row>
     <row r="178" spans="3:27" x14ac:dyDescent="0.2">
@@ -17291,7 +17300,7 @@
         <v>43</v>
       </c>
       <c r="AA179" t="s">
-        <v>43</v>
+        <v>277</v>
       </c>
     </row>
     <row r="180" spans="3:27" x14ac:dyDescent="0.2">
@@ -17362,7 +17371,7 @@
         <v>43</v>
       </c>
       <c r="AA180" t="s">
-        <v>43</v>
+        <v>277</v>
       </c>
     </row>
     <row r="181" spans="3:27" x14ac:dyDescent="0.2">

--- a/2027.xlsx
+++ b/2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2025/Drucken/Section Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{D787E4CA-058C-F043-AC37-9558793B5EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{E27105E3-5FF0-1E44-A7AD-7E18EFC46BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1830" windowWidth="23040" windowHeight="7338" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4151" uniqueCount="1434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4151" uniqueCount="1433">
   <si>
     <t>Katalog-Nr</t>
   </si>
@@ -14467,7 +14467,7 @@
         <v>43</v>
       </c>
       <c r="AA138" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
     </row>
     <row r="139" spans="3:27" x14ac:dyDescent="0.2">
@@ -14538,7 +14538,7 @@
         <v>43</v>
       </c>
       <c r="AA139" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
     </row>
     <row r="140" spans="3:27" x14ac:dyDescent="0.2">
@@ -14609,7 +14609,7 @@
         <v>43</v>
       </c>
       <c r="AA140" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
     </row>
     <row r="141" spans="3:27" x14ac:dyDescent="0.2">
@@ -14677,7 +14677,7 @@
         <v>43</v>
       </c>
       <c r="AA141" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
     </row>
     <row r="142" spans="3:27" x14ac:dyDescent="0.2">
@@ -14748,7 +14748,7 @@
         <v>43</v>
       </c>
       <c r="AA142" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
     </row>
     <row r="143" spans="3:27" x14ac:dyDescent="0.2">
@@ -14816,7 +14816,7 @@
         <v>43</v>
       </c>
       <c r="AA143" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
     </row>
     <row r="144" spans="3:27" x14ac:dyDescent="0.2">
@@ -14881,7 +14881,7 @@
         <v>43</v>
       </c>
       <c r="AA144" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
     </row>
     <row r="145" spans="3:27" x14ac:dyDescent="0.2">
@@ -14958,7 +14958,7 @@
         <v>43</v>
       </c>
       <c r="AA145" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
     </row>
     <row r="146" spans="3:27" x14ac:dyDescent="0.2">

--- a/2027.xlsx
+++ b/2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2025/Drucken/Section Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{E27105E3-5FF0-1E44-A7AD-7E18EFC46BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{1D11949E-C1B8-6E42-919A-FCFFF8F7FC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1830" windowWidth="23040" windowHeight="7338" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4151" uniqueCount="1433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4268" uniqueCount="1433">
   <si>
     <t>Katalog-Nr</t>
   </si>
@@ -5405,9 +5405,6 @@
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
       <c r="C10" t="s">
         <v>27</v>
       </c>
@@ -5550,9 +5547,6 @@
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>27</v>
-      </c>
       <c r="C12" t="s">
         <v>27</v>
       </c>
@@ -5630,6 +5624,9 @@
       <c r="A13" t="s">
         <v>27</v>
       </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
       <c r="D13" t="s">
         <v>108</v>
       </c>
@@ -5698,6 +5695,9 @@
       <c r="A14" t="s">
         <v>27</v>
       </c>
+      <c r="B14" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="C14" t="s">
         <v>27</v>
       </c>
@@ -5763,6 +5763,9 @@
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
       <c r="D15" t="s">
         <v>150</v>
       </c>
@@ -5834,6 +5837,12 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
       <c r="D16" t="s">
         <v>163</v>
       </c>
@@ -5904,7 +5913,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D17" t="s">
         <v>173</v>
       </c>
@@ -5975,7 +5984,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
       <c r="D18" t="s">
         <v>185</v>
       </c>
@@ -6040,7 +6052,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
       <c r="C19" t="s">
         <v>27</v>
       </c>
@@ -6114,7 +6129,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
       <c r="D20" t="s">
         <v>205</v>
       </c>
@@ -6185,7 +6203,13 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
       <c r="D21" t="s">
         <v>210</v>
       </c>
@@ -6256,7 +6280,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
       <c r="D22" t="s">
         <v>219</v>
       </c>
@@ -6321,7 +6348,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
       <c r="D23" t="s">
         <v>225</v>
       </c>
@@ -6386,7 +6416,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D24" t="s">
         <v>235</v>
       </c>
@@ -6454,7 +6484,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
       <c r="D25" t="s">
         <v>240</v>
       </c>
@@ -6525,7 +6558,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C26" t="s">
         <v>27</v>
       </c>
@@ -6599,7 +6632,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
       <c r="C27" t="s">
         <v>27</v>
       </c>
@@ -6673,7 +6709,13 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>27</v>
+      </c>
       <c r="C28" t="s">
         <v>27</v>
       </c>
@@ -6747,7 +6789,10 @@
         <v>162</v>
       </c>
     </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
       <c r="D29" t="s">
         <v>278</v>
       </c>
@@ -6815,7 +6860,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D30" t="s">
         <v>288</v>
       </c>
@@ -6880,7 +6925,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C31" t="s">
         <v>27</v>
       </c>
@@ -6954,7 +6999,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D32" t="s">
         <v>304</v>
       </c>
@@ -7025,7 +7070,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="33" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D33" t="s">
         <v>314</v>
       </c>
@@ -7096,7 +7141,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>27</v>
+      </c>
       <c r="D34" t="s">
         <v>320</v>
       </c>
@@ -7167,7 +7215,13 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" t="s">
+        <v>27</v>
+      </c>
       <c r="C35" t="s">
         <v>27</v>
       </c>
@@ -7241,7 +7295,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>27</v>
+      </c>
       <c r="D36" t="s">
         <v>329</v>
       </c>
@@ -7306,7 +7363,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>27</v>
+      </c>
       <c r="C37" t="s">
         <v>27</v>
       </c>
@@ -7380,7 +7440,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>27</v>
+      </c>
       <c r="D38" t="s">
         <v>338</v>
       </c>
@@ -7451,7 +7514,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D39" t="s">
         <v>347</v>
       </c>
@@ -7522,7 +7585,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>27</v>
+      </c>
       <c r="D40" t="s">
         <v>359</v>
       </c>
@@ -7587,7 +7653,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C41" t="s">
         <v>27</v>
       </c>
@@ -7664,7 +7730,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="42" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D42" t="s">
         <v>378</v>
       </c>
@@ -7735,7 +7801,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="43" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D43" t="s">
         <v>385</v>
       </c>
@@ -7800,7 +7866,13 @@
         <v>162</v>
       </c>
     </row>
-    <row r="44" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B44" t="s">
+        <v>27</v>
+      </c>
       <c r="D44" t="s">
         <v>390</v>
       </c>
@@ -7865,7 +7937,10 @@
         <v>162</v>
       </c>
     </row>
-    <row r="45" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="D45" t="s">
         <v>396</v>
       </c>
@@ -7930,7 +8005,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="46" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C46" t="s">
         <v>27</v>
       </c>
@@ -8004,7 +8079,13 @@
         <v>162</v>
       </c>
     </row>
-    <row r="47" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" t="s">
+        <v>27</v>
+      </c>
       <c r="D47" t="s">
         <v>407</v>
       </c>
@@ -8075,7 +8156,10 @@
         <v>162</v>
       </c>
     </row>
-    <row r="48" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
+        <v>27</v>
+      </c>
       <c r="D48" t="s">
         <v>412</v>
       </c>
@@ -8140,7 +8224,13 @@
         <v>162</v>
       </c>
     </row>
-    <row r="49" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>27</v>
+      </c>
+      <c r="B49" t="s">
+        <v>27</v>
+      </c>
       <c r="D49" t="s">
         <v>416</v>
       </c>
@@ -8205,7 +8295,13 @@
         <v>162</v>
       </c>
     </row>
-    <row r="50" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>27</v>
+      </c>
+      <c r="B50" t="s">
+        <v>27</v>
+      </c>
       <c r="D50" t="s">
         <v>421</v>
       </c>
@@ -8276,7 +8372,10 @@
         <v>162</v>
       </c>
     </row>
-    <row r="51" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>27</v>
+      </c>
       <c r="D51" t="s">
         <v>426</v>
       </c>
@@ -8341,7 +8440,13 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="52" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>27</v>
+      </c>
+      <c r="B52" t="s">
+        <v>27</v>
+      </c>
       <c r="C52" t="s">
         <v>27</v>
       </c>
@@ -8415,7 +8520,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="53" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B53" t="s">
+        <v>27</v>
+      </c>
       <c r="D53" t="s">
         <v>439</v>
       </c>
@@ -8486,7 +8594,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="54" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>27</v>
+      </c>
       <c r="D54" t="s">
         <v>450</v>
       </c>
@@ -8557,7 +8668,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="55" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
         <v>27</v>
       </c>
@@ -8634,7 +8745,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="56" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B56" t="s">
+        <v>27</v>
+      </c>
       <c r="D56" t="s">
         <v>461</v>
       </c>
@@ -8699,7 +8813,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="57" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D57" t="s">
         <v>465</v>
       </c>
@@ -8773,7 +8887,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="58" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
         <v>27</v>
       </c>
@@ -8850,7 +8964,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="59" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>27</v>
+      </c>
       <c r="B59" t="s">
         <v>27</v>
       </c>
@@ -8930,10 +9047,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="60" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B60" t="s">
-        <v>27</v>
-      </c>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C60" t="s">
         <v>27</v>
       </c>
@@ -8995,7 +9109,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
         <v>27</v>
       </c>
@@ -9075,7 +9189,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="62" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D62" t="s">
         <v>511</v>
       </c>
@@ -9146,7 +9260,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="63" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
         <v>27</v>
       </c>
@@ -9223,7 +9337,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="64" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
         <v>27</v>
       </c>
@@ -9300,7 +9414,10 @@
         <v>162</v>
       </c>
     </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B65" t="s">
+        <v>27</v>
+      </c>
       <c r="D65" t="s">
         <v>543</v>
       </c>
@@ -9371,7 +9488,10 @@
         <v>162</v>
       </c>
     </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>27</v>
+      </c>
       <c r="B66" t="s">
         <v>27</v>
       </c>
@@ -9448,8 +9568,8 @@
         <v>162</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B67" t="s">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
         <v>27</v>
       </c>
       <c r="C67" t="s">
@@ -9513,7 +9633,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>27</v>
+      </c>
       <c r="D68" t="s">
         <v>565</v>
       </c>
@@ -9572,10 +9695,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B69" t="s">
-        <v>27</v>
-      </c>
+    <row r="69" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C69" t="s">
         <v>27</v>
       </c>
@@ -9640,10 +9760,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B70" t="s">
-        <v>27</v>
-      </c>
+    <row r="70" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C70" t="s">
         <v>27</v>
       </c>
@@ -9720,7 +9837,10 @@
         <v>162</v>
       </c>
     </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>27</v>
+      </c>
       <c r="D71" t="s">
         <v>592</v>
       </c>
@@ -9791,10 +9911,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B72" t="s">
-        <v>27</v>
-      </c>
+    <row r="72" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C72" t="s">
         <v>27</v>
       </c>
@@ -9868,7 +9985,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D73" t="s">
         <v>603</v>
       </c>
@@ -9939,10 +10056,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B74" t="s">
-        <v>27</v>
-      </c>
+    <row r="74" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C74" t="s">
         <v>27</v>
       </c>
@@ -10016,7 +10130,10 @@
         <v>162</v>
       </c>
     </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>27</v>
+      </c>
       <c r="B75" t="s">
         <v>27</v>
       </c>
@@ -10081,10 +10198,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B76" t="s">
-        <v>27</v>
-      </c>
+    <row r="76" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C76" t="s">
         <v>27</v>
       </c>
@@ -10146,7 +10260,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B77" t="s">
         <v>27</v>
       </c>
@@ -10223,7 +10337,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="78" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B78" t="s">
+        <v>27</v>
+      </c>
       <c r="D78" t="s">
         <v>647</v>
       </c>
@@ -10294,7 +10411,13 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>27</v>
+      </c>
+      <c r="B79" t="s">
+        <v>27</v>
+      </c>
       <c r="D79" t="s">
         <v>652</v>
       </c>
@@ -10365,7 +10488,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B80" t="s">
+        <v>27</v>
+      </c>
       <c r="D80" t="s">
         <v>660</v>
       </c>
@@ -10436,7 +10562,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="81" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>27</v>
+      </c>
       <c r="D81" t="s">
         <v>666</v>
       </c>
@@ -10507,8 +10636,8 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="82" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B82" t="s">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
         <v>27</v>
       </c>
       <c r="C82" t="s">
@@ -10575,8 +10704,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="83" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B83" t="s">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
         <v>27</v>
       </c>
       <c r="C83" t="s">
@@ -10652,7 +10781,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="84" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>27</v>
+      </c>
       <c r="D84" t="s">
         <v>688</v>
       </c>
@@ -10717,7 +10849,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="85" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B85" t="s">
+        <v>27</v>
+      </c>
       <c r="D85" t="s">
         <v>695</v>
       </c>
@@ -10788,7 +10923,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="86" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B86" t="s">
         <v>27</v>
       </c>
@@ -10865,7 +11000,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="87" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D87" t="s">
         <v>705</v>
       </c>
@@ -10936,7 +11071,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="88" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D88" t="s">
         <v>717</v>
       </c>
@@ -10995,7 +11130,13 @@
         <v>43</v>
       </c>
     </row>
-    <row r="89" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>27</v>
+      </c>
+      <c r="B89" t="s">
+        <v>27</v>
+      </c>
       <c r="D89" t="s">
         <v>726</v>
       </c>
@@ -11066,7 +11207,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="90" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>27</v>
+      </c>
       <c r="D90" t="s">
         <v>736</v>
       </c>
@@ -11137,7 +11281,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="91" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D91" t="s">
         <v>741</v>
       </c>
@@ -11208,7 +11352,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="92" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B92" t="s">
         <v>27</v>
       </c>
@@ -11285,8 +11429,8 @@
         <v>57</v>
       </c>
     </row>
-    <row r="93" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B93" t="s">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
         <v>27</v>
       </c>
       <c r="C93" t="s">
@@ -11362,7 +11506,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="94" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B94" t="s">
+        <v>27</v>
+      </c>
       <c r="D94" t="s">
         <v>766</v>
       </c>
@@ -11433,7 +11580,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="95" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B95" t="s">
+        <v>27</v>
+      </c>
       <c r="D95" t="s">
         <v>772</v>
       </c>
@@ -11504,7 +11654,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B96" t="s">
+        <v>27</v>
+      </c>
       <c r="D96" t="s">
         <v>777</v>
       </c>
@@ -11575,7 +11728,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B97" t="s">
+        <v>27</v>
+      </c>
       <c r="C97" t="s">
         <v>27</v>
       </c>
@@ -11649,7 +11805,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D98" t="s">
         <v>786</v>
       </c>
@@ -11711,7 +11867,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C99" t="s">
         <v>27</v>
       </c>
@@ -11785,7 +11941,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>27</v>
+      </c>
       <c r="D100" t="s">
         <v>800</v>
       </c>
@@ -11856,7 +12015,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C101" t="s">
         <v>27</v>
       </c>
@@ -11930,7 +12089,13 @@
         <v>43</v>
       </c>
     </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>27</v>
+      </c>
+      <c r="B102" t="s">
+        <v>27</v>
+      </c>
       <c r="D102" t="s">
         <v>822</v>
       </c>
@@ -11995,7 +12160,13 @@
         <v>43</v>
       </c>
     </row>
-    <row r="103" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>27</v>
+      </c>
+      <c r="B103" t="s">
+        <v>27</v>
+      </c>
       <c r="D103" t="s">
         <v>832</v>
       </c>
@@ -12060,7 +12231,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="104" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>27</v>
+      </c>
       <c r="C104" t="s">
         <v>27</v>
       </c>
@@ -12134,7 +12308,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="105" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>27</v>
+      </c>
       <c r="C105" t="s">
         <v>27</v>
       </c>
@@ -12208,7 +12385,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="106" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B106" t="s">
+        <v>27</v>
+      </c>
       <c r="C106" t="s">
         <v>27</v>
       </c>
@@ -12285,7 +12465,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="107" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D107" t="s">
         <v>857</v>
       </c>
@@ -12350,7 +12530,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="108" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D108" t="s">
         <v>862</v>
       </c>
@@ -12409,7 +12589,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="109" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D109" t="s">
         <v>874</v>
       </c>
@@ -12480,7 +12660,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="110" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>27</v>
+      </c>
       <c r="D110" t="s">
         <v>885</v>
       </c>
@@ -12551,7 +12734,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="111" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>27</v>
+      </c>
       <c r="C111" t="s">
         <v>27</v>
       </c>
@@ -12628,7 +12814,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="112" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B112" t="s">
+        <v>27</v>
+      </c>
       <c r="C112" t="s">
         <v>27</v>
       </c>
@@ -12702,7 +12891,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="113" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C113" t="s">
         <v>27</v>
       </c>
@@ -12776,7 +12965,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="114" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>27</v>
+      </c>
       <c r="D114" t="s">
         <v>926</v>
       </c>
@@ -12841,7 +13033,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="115" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D115" t="s">
         <v>937</v>
       </c>
@@ -12906,7 +13098,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="116" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D116" t="s">
         <v>948</v>
       </c>
@@ -12971,7 +13163,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="117" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D117" t="s">
         <v>958</v>
       </c>
@@ -13042,7 +13234,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="118" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D118" t="s">
         <v>968</v>
       </c>
@@ -13110,7 +13302,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="119" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B119" t="s">
+        <v>27</v>
+      </c>
       <c r="D119" t="s">
         <v>978</v>
       </c>
@@ -13175,7 +13370,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="120" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B120" t="s">
+        <v>27</v>
+      </c>
       <c r="D120" t="s">
         <v>983</v>
       </c>
@@ -13240,7 +13438,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="121" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B121" t="s">
+        <v>27</v>
+      </c>
       <c r="D121" t="s">
         <v>988</v>
       </c>
@@ -13305,7 +13506,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="122" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>27</v>
+      </c>
       <c r="D122" t="s">
         <v>991</v>
       </c>
@@ -13376,7 +13580,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="123" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D123" t="s">
         <v>1001</v>
       </c>
@@ -13447,7 +13651,13 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="124" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>27</v>
+      </c>
+      <c r="B124" t="s">
+        <v>27</v>
+      </c>
       <c r="D124" t="s">
         <v>1009</v>
       </c>
@@ -13518,7 +13728,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="125" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>27</v>
+      </c>
       <c r="D125" t="s">
         <v>1019</v>
       </c>
@@ -13589,7 +13802,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="126" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>27</v>
+      </c>
       <c r="C126" t="s">
         <v>27</v>
       </c>
@@ -13663,7 +13879,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="127" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>27</v>
+      </c>
       <c r="D127" t="s">
         <v>1034</v>
       </c>
@@ -13734,7 +13953,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="128" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B128" t="s">
+        <v>27</v>
+      </c>
       <c r="D128" t="s">
         <v>1039</v>
       </c>
@@ -13793,7 +14015,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="129" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D129" t="s">
         <v>1045</v>
       </c>
@@ -13858,7 +14080,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="130" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C130" t="s">
         <v>27</v>
       </c>
@@ -13932,7 +14154,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="131" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C131" t="s">
         <v>27</v>
       </c>
@@ -13994,7 +14216,13 @@
         <v>43</v>
       </c>
     </row>
-    <row r="132" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>27</v>
+      </c>
+      <c r="B132" t="s">
+        <v>27</v>
+      </c>
       <c r="D132" t="s">
         <v>1061</v>
       </c>
@@ -14065,7 +14293,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="133" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>27</v>
+      </c>
       <c r="D133" t="s">
         <v>1066</v>
       </c>
@@ -14136,7 +14367,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="134" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B134" t="s">
+        <v>27</v>
+      </c>
       <c r="D134" t="s">
         <v>1070</v>
       </c>
@@ -14195,7 +14429,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="135" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B135" t="s">
+        <v>27</v>
+      </c>
       <c r="C135" t="s">
         <v>27</v>
       </c>
@@ -14269,7 +14506,13 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="136" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>27</v>
+      </c>
+      <c r="B136" t="s">
+        <v>27</v>
+      </c>
       <c r="D136" t="s">
         <v>1084</v>
       </c>
@@ -14340,7 +14583,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="137" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B137" t="s">
+        <v>27</v>
+      </c>
       <c r="D137" t="s">
         <v>1089</v>
       </c>
@@ -14399,7 +14645,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="138" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C138" t="s">
         <v>27</v>
       </c>
@@ -14470,7 +14716,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="139" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C139" t="s">
         <v>27</v>
       </c>
@@ -14541,7 +14787,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="140" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C140" t="s">
         <v>27</v>
       </c>
@@ -14612,7 +14858,10 @@
         <v>35</v>
       </c>
     </row>
-    <row r="141" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>27</v>
+      </c>
       <c r="D141" t="s">
         <v>1126</v>
       </c>
@@ -14680,7 +14929,10 @@
         <v>35</v>
       </c>
     </row>
-    <row r="142" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B142" t="s">
+        <v>27</v>
+      </c>
       <c r="C142" t="s">
         <v>27</v>
       </c>
@@ -14751,7 +15003,13 @@
         <v>35</v>
       </c>
     </row>
-    <row r="143" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>27</v>
+      </c>
+      <c r="B143" t="s">
+        <v>27</v>
+      </c>
       <c r="D143" t="s">
         <v>1135</v>
       </c>
@@ -14819,7 +15077,10 @@
         <v>35</v>
       </c>
     </row>
-    <row r="144" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>27</v>
+      </c>
       <c r="D144" t="s">
         <v>1140</v>
       </c>
@@ -14884,7 +15145,10 @@
         <v>35</v>
       </c>
     </row>
-    <row r="145" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>27</v>
+      </c>
       <c r="C145" t="s">
         <v>27</v>
       </c>
@@ -14961,7 +15225,13 @@
         <v>35</v>
       </c>
     </row>
-    <row r="146" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>27</v>
+      </c>
+      <c r="B146" t="s">
+        <v>27</v>
+      </c>
       <c r="C146" t="s">
         <v>27</v>
       </c>
@@ -15023,7 +15293,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="147" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C147" t="s">
         <v>27</v>
       </c>
@@ -15094,7 +15364,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="148" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C148" t="s">
         <v>27</v>
       </c>
@@ -15168,7 +15438,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="149" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C149" t="s">
         <v>27</v>
       </c>
@@ -15242,7 +15512,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="150" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B150" t="s">
+        <v>27</v>
+      </c>
       <c r="C150" t="s">
         <v>27</v>
       </c>
@@ -15313,7 +15586,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="151" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>27</v>
+      </c>
       <c r="C151" t="s">
         <v>27</v>
       </c>
@@ -15387,7 +15663,13 @@
         <v>43</v>
       </c>
     </row>
-    <row r="152" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>27</v>
+      </c>
+      <c r="B152" t="s">
+        <v>27</v>
+      </c>
       <c r="D152" t="s">
         <v>1197</v>
       </c>
@@ -15458,7 +15740,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="153" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B153" t="s">
+        <v>27</v>
+      </c>
       <c r="D153" t="s">
         <v>1203</v>
       </c>
@@ -15517,7 +15802,10 @@
         <v>35</v>
       </c>
     </row>
-    <row r="154" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B154" t="s">
+        <v>27</v>
+      </c>
       <c r="D154" t="s">
         <v>1214</v>
       </c>
@@ -15582,7 +15870,13 @@
         <v>277</v>
       </c>
     </row>
-    <row r="155" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>27</v>
+      </c>
+      <c r="B155" t="s">
+        <v>27</v>
+      </c>
       <c r="D155" t="s">
         <v>1224</v>
       </c>
@@ -15647,7 +15941,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="156" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C156" t="s">
         <v>27</v>
       </c>
@@ -15709,7 +16003,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="157" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C157" t="s">
         <v>27</v>
       </c>
@@ -15783,7 +16077,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="158" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C158" t="s">
         <v>27</v>
       </c>
@@ -15845,7 +16139,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="159" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C159" t="s">
         <v>27</v>
       </c>
@@ -15922,7 +16216,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="160" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B160" t="s">
+        <v>27</v>
+      </c>
       <c r="C160" t="s">
         <v>27</v>
       </c>
@@ -15996,7 +16293,13 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="161" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>27</v>
+      </c>
+      <c r="B161" t="s">
+        <v>27</v>
+      </c>
       <c r="C161" t="s">
         <v>27</v>
       </c>
@@ -16058,7 +16361,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="162" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C162" t="s">
         <v>27</v>
       </c>
@@ -16120,7 +16423,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="163" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>27</v>
+      </c>
       <c r="C163" t="s">
         <v>27</v>
       </c>
@@ -16191,7 +16497,13 @@
         <v>277</v>
       </c>
     </row>
-    <row r="164" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>27</v>
+      </c>
+      <c r="B164" t="s">
+        <v>27</v>
+      </c>
       <c r="D164" t="s">
         <v>1298</v>
       </c>
@@ -16262,7 +16574,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="165" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>27</v>
+      </c>
       <c r="C165" t="s">
         <v>27</v>
       </c>
@@ -16336,7 +16651,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="166" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>27</v>
+      </c>
       <c r="C166" t="s">
         <v>27</v>
       </c>
@@ -16410,7 +16728,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="167" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D167" t="s">
         <v>1315</v>
       </c>
@@ -16481,7 +16799,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="168" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B168" t="s">
+        <v>27</v>
+      </c>
       <c r="D168" t="s">
         <v>1319</v>
       </c>
@@ -16540,7 +16861,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="169" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C169" t="s">
         <v>27</v>
       </c>
@@ -16602,7 +16923,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="170" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B170" t="s">
+        <v>27</v>
+      </c>
       <c r="D170" t="s">
         <v>1335</v>
       </c>
@@ -16661,7 +16985,13 @@
         <v>162</v>
       </c>
     </row>
-    <row r="171" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>27</v>
+      </c>
+      <c r="B171" t="s">
+        <v>27</v>
+      </c>
       <c r="C171" t="s">
         <v>27</v>
       </c>
@@ -16735,7 +17065,13 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="172" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
+        <v>27</v>
+      </c>
+      <c r="B172" t="s">
+        <v>27</v>
+      </c>
       <c r="D172" t="s">
         <v>1346</v>
       </c>
@@ -16806,7 +17142,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="173" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B173" t="s">
+        <v>27</v>
+      </c>
       <c r="D173" t="s">
         <v>1357</v>
       </c>
@@ -16877,7 +17216,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="174" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C174" t="s">
         <v>27</v>
       </c>
@@ -16951,7 +17290,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="175" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>27</v>
+      </c>
       <c r="C175" t="s">
         <v>27</v>
       </c>
@@ -17025,7 +17367,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="176" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D176" t="s">
         <v>1374</v>
       </c>
@@ -17096,7 +17438,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="177" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C177" t="s">
         <v>27</v>
       </c>
@@ -17170,7 +17512,10 @@
         <v>277</v>
       </c>
     </row>
-    <row r="178" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B178" t="s">
+        <v>27</v>
+      </c>
       <c r="C178" t="s">
         <v>27</v>
       </c>
@@ -17232,7 +17577,10 @@
         <v>162</v>
       </c>
     </row>
-    <row r="179" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B179" t="s">
+        <v>27</v>
+      </c>
       <c r="D179" t="s">
         <v>1397</v>
       </c>
@@ -17303,7 +17651,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="180" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="180" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C180" t="s">
         <v>27</v>
       </c>
@@ -17374,7 +17722,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="181" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D181" t="s">
         <v>1406</v>
       </c>
@@ -17433,7 +17781,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="182" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B182" t="s">
+        <v>27</v>
+      </c>
       <c r="D182" t="s">
         <v>1411</v>
       </c>
@@ -17492,7 +17843,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="183" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D183" t="s">
         <v>1416</v>
       </c>
